--- a/光伏配储项目/电价数据/2026/仁安站.xlsx
+++ b/光伏配储项目/电价数据/2026/仁安站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50979</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7406200000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57089</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.57204</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.49662</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49169</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43753</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45435</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43869</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42302</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41916</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40874</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42062</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44384</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27688</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.28559</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11153</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09095</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.09693</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08178000000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.10581</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04168</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.08242000000000001</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.09667000000000001</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.09612999999999999</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.07373</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08935</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06304999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.04792</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14697</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21435</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23807</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25291</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.19985</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.06802</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00236</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.26032</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.12902</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.26563</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26227</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.25787</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.17723</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.27282</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5094</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.36446</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.79734</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.57733</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42704</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43899</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41556</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5632999999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.43754</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.58656</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79032</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6337699999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.70621</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.76027</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41478</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65306</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.60105</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.62629</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.57578</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.56609</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6297200000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.59946</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46418</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48496</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42556</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.68145</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.5933</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75525</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.13894</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.81224</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5253</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5196900000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50547</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50742</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49134</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50282</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59868</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.6774</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43119</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.40733</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49977</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.14475</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.46591</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.74888</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.8630800000000001</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.72538</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.47463</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.10016</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.25874</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.24083</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40995</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.52199</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.64285</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.49636</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68475</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.74748</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.75546</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.49263</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.47932</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.80218</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.48007</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.8612000000000001</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.58712</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43907</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43274</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41034</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33451</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52325</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4691</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43267</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44875</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47389</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44868</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19006</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26535</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.46187</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.49748</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.46854</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.14162</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.29191</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.24368</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.27545</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27568</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28204</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.43684</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.47583</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.49709</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.58466</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.47862</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.58788</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.42727</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.42629</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.44667</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.4329</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34258</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46011</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26641</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.14299</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.1995</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.14893</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.24849</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.20212</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.50654</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.04872</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.10647</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28666</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.14818</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.15643</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.48517</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.04957</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.11587</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.20714</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.23186</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.23102</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24781</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21904</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14913</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.27092</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28262</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41714</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.54937</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45223</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.44447</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29659</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04389</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04693</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04394</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04404</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04411</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04864</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04886</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03539</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04759</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04436</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04176</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.03962</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04015</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04116</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04071</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03851</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04234</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.0458</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04113</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.0419</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.0469</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04143</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04509000000000001</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.2193</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04894</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05471</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05582</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00094</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15014</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.04122</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.10171</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40867</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46767</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35117</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66673</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44695</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04323</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04679999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04568</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03129</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04201</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10653</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00017</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03792</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04325</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0451</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04095</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04493</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04509000000000001</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04313</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04386</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04027</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04231</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04443</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04722</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04752</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20035</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14315</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26932</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33598</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31842</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40522</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28163</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28853</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27163</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27144</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17274</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15898</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17136</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14806</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15979</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15898</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23678</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22694</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26948</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28624</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27065</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28137</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45223</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41689</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41368</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15672</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29228</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49793</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78098</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9203</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49449</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91734</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.87285</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.30147</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89712</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6332300000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19653</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87341</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5502899999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.34054</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03956</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.54051</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79925</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53095</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78128</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78413</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87779</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87821</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5009100000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4099</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45882</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21701</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87918</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55123</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6317699999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5408099999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50057</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45706</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42545</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43892</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41497</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43401</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40555</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58745</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59633</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6024299999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66935</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46523</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41654</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5774199999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87619</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63506</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85182</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.83365</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.85991</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43986</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.44072</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41316</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45303</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39194</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35354</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93562</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4710299999999999</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.44271</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5022099999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50087</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28947</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16489</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26188</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19946</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27732</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27623</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43656</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44869</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42084</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5980599999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89044</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.32418</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1303</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69465</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7834099999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64661</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57814</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44881</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44805</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49706</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43761</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43546</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41322</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42175</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.4977200000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43189</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42639</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44844</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42149</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.50098</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5591799999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25002</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.54474</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.12596</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27939</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28645</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39886</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57653</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46141</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7634299999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46254</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43791</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42362</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32459</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28023</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28594</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23123</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14616</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15028</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28779</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15779</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14576</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14241</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14559</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.26165</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14662</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27059</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14482</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.11617</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10744</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.13844</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14138</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14603</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28185</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44817</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44313</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43818</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44233</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44204</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5367999999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46594</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42179</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26113</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19454</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2468</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23827</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23797</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35998</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43219</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.00521</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25055</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.25685</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.08902</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44616</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44695</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71111</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.51528</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29108</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34968</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.41133</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43716</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41012</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6773899999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7857000000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47317</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45759</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34854</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41584</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26501</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14607</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.1987</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25689</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21829</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26202</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28485</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27813</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14999</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29307</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43317</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42383</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.61825</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6517999999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.67636</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48982</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7364700000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.52158</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8786799999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.46905</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48227</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48348</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43074</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42888</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36017</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49126</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.55206</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.49689</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42159</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40304</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40756</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41904</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41417</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40675</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41655</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40164</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41418</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4030899999999999</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44756</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.4553</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56153</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49646</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44773</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.55676</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.46173</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44128</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42533</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42461</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.51664</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.44973</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29717</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28769</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.64028</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15702</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28021</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43323</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48841</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43539</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.51007</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5364500000000001</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.60229</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.7705299999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.78713</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.94492</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7139500000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8029400000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5967</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.54923</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.91096</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.8359099999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62863</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.69997</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45027</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47113</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.50264</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47841</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.48964</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.56316</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42881</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46683</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45126</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43143</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45494</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42949</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46762</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40606</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18151</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44916</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46456</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11075</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.1811</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41564</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42713</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40897</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40809</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40146</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36566</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27035</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22862</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28884</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23073</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28891</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25054</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25324</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13968</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25004</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25179</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28766</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16896</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18079</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27273</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22764</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24797</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26145</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23153</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27512</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35077</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25197</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21299</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20831</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00023</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02675</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04978</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10899</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01325</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03977</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04978</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02266</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04501</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04908</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04881</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02705</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03316</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.11399</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04979</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04979</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00272</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04979</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03267</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04978</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04278</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17101</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20367</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.24132</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2794700000000001</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26997</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27466</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.28986</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.15953</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.59877</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.18725</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.2846</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.26046</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.25163</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.27671</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26566</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.23564</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26335</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25679</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28736</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27971</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28621</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.28624</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.24144</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.18441</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6615700000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.66743</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.67618</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.59876</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.17614</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09314</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24394</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.18934</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.14053</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.14617</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.10517</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23271</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.12906</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.05283</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.06875000000000001</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.11846</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.18614</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02395</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.13855</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.14329</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.16221</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.009970000000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.12202</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.12729</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.12871</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25331</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27334</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3239</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.08470999999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.47669</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.54386</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41748</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.45727</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45567</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43847</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.13918</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27384</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27005</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27752</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.41516</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33292</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.6047100000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5802999999999999</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.52719</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26048</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28305</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41436</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.50348</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.5167999999999999</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45176</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46281</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41171</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.43857</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.43306</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.46702</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.4035899999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.47844</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.41215</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.66206</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.5041100000000001</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.37456</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47803</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.42971</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26437</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.46467</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.44349</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42652</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42602</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5099</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5948</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.59229</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46437</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51066</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.55884</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.56829</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52498</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.9678</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8610399999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.59973</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5948300000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.45912</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3791</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27122</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24538</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27359</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.28373</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.12439</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.21024</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.18153</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05509</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.13052</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02344</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19391</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16275</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00415</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25493</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15362</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05148</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04731</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06059</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.14558</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.06870999999999999</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05205</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.16947</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.13739</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.16344</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.26102</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.28276</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26235</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41909</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42346</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.44439</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.5139600000000001</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38048</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.96634</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.4822</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43168</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38798</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38251</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27671</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.27034</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.27176</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11468</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01808</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01818</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01727</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03823</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.17548</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03971</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00598</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04549</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01437</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01278</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01433</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16126</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.26116</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04415</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.24558</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.16059</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.25679</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.47968</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5508099999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.5679299999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3755</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.59237</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.43793</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26354</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23706</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21476</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23835</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24212</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11749</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15597</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04951</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.04012</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04779</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04682</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04437</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08114</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02887</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06511</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.10017</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17712</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20176</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12436</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.26987</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.23688</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12739</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04862</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26791</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.15215</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11993</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.24126</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19316</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.25017</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.25329</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.21106</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41037</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40849</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38438</v>
       </c>
     </row>
   </sheetData>
